--- a/HumanMetbaolicA1C.xlsx
+++ b/HumanMetbaolicA1C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3B10314-22F5-4354-8115-88A95A5ACC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D203BE96-EBBA-4F4B-980A-532C932F6351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23116E1F-C70A-422D-B7F6-A9521DD66DAE}"/>
   </bookViews>
